--- a/Physics_Labs/1_sem/Lab114/data.xlsx
+++ b/Physics_Labs/1_sem/Lab114/data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Library/Mobile Documents/com~apple~CloudDocs/Лабы/Labs/Physics_Labs/1_sem/Lab114/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/git/Labs/Physics_Labs/1_sem/Lab114/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA99334-7F63-DE4F-A01F-E0598FC651B2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207E6F89-634C-1E4A-8E57-D7E7425622F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="460" windowWidth="24940" windowHeight="14480" xr2:uid="{2457A769-9EFE-3640-A5B0-534005E46BD2}"/>
+    <workbookView xWindow="14400" yWindow="740" windowWidth="15840" windowHeight="18900" activeTab="1" xr2:uid="{2457A769-9EFE-3640-A5B0-534005E46BD2}"/>
   </bookViews>
   <sheets>
     <sheet name="20 sec" sheetId="1" r:id="rId1"/>
+    <sheet name="40 sec" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -66,7 +67,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -82,9 +83,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -122,7 +123,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -228,7 +229,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -370,7 +371,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1024,4 +1025,334 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA11FEC7-D917-9743-AFCB-DE83D1F6BE07}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1">
+        <v>49</v>
+      </c>
+      <c r="B1">
+        <v>57</v>
+      </c>
+      <c r="C1">
+        <v>44</v>
+      </c>
+      <c r="D1">
+        <v>41</v>
+      </c>
+      <c r="E1">
+        <v>54</v>
+      </c>
+      <c r="F1">
+        <v>51</v>
+      </c>
+      <c r="G1">
+        <v>55</v>
+      </c>
+      <c r="H1">
+        <v>51</v>
+      </c>
+      <c r="I1">
+        <v>57</v>
+      </c>
+      <c r="J1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>55</v>
+      </c>
+      <c r="B2">
+        <v>61</v>
+      </c>
+      <c r="C2">
+        <v>64</v>
+      </c>
+      <c r="D2">
+        <v>56</v>
+      </c>
+      <c r="E2">
+        <v>58</v>
+      </c>
+      <c r="F2">
+        <v>52</v>
+      </c>
+      <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>47</v>
+      </c>
+      <c r="I2">
+        <v>49</v>
+      </c>
+      <c r="J2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>52</v>
+      </c>
+      <c r="B3">
+        <v>40</v>
+      </c>
+      <c r="C3">
+        <v>64</v>
+      </c>
+      <c r="D3">
+        <v>53</v>
+      </c>
+      <c r="E3">
+        <v>55</v>
+      </c>
+      <c r="F3">
+        <v>54</v>
+      </c>
+      <c r="G3">
+        <v>48</v>
+      </c>
+      <c r="H3">
+        <v>51</v>
+      </c>
+      <c r="I3">
+        <v>55</v>
+      </c>
+      <c r="J3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>56</v>
+      </c>
+      <c r="B4">
+        <v>41</v>
+      </c>
+      <c r="C4">
+        <v>63</v>
+      </c>
+      <c r="D4">
+        <v>52</v>
+      </c>
+      <c r="E4">
+        <v>57</v>
+      </c>
+      <c r="F4">
+        <v>52</v>
+      </c>
+      <c r="G4">
+        <v>51</v>
+      </c>
+      <c r="H4">
+        <v>60</v>
+      </c>
+      <c r="I4">
+        <v>40</v>
+      </c>
+      <c r="J4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>50</v>
+      </c>
+      <c r="B5">
+        <v>53</v>
+      </c>
+      <c r="C5">
+        <v>52</v>
+      </c>
+      <c r="D5">
+        <v>52</v>
+      </c>
+      <c r="E5">
+        <v>58</v>
+      </c>
+      <c r="F5">
+        <v>52</v>
+      </c>
+      <c r="G5">
+        <v>56</v>
+      </c>
+      <c r="H5">
+        <v>49</v>
+      </c>
+      <c r="I5">
+        <v>59</v>
+      </c>
+      <c r="J5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>54</v>
+      </c>
+      <c r="B6">
+        <v>55</v>
+      </c>
+      <c r="C6">
+        <v>59</v>
+      </c>
+      <c r="D6">
+        <v>64</v>
+      </c>
+      <c r="E6">
+        <v>58</v>
+      </c>
+      <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>46</v>
+      </c>
+      <c r="I6">
+        <v>42</v>
+      </c>
+      <c r="J6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>57</v>
+      </c>
+      <c r="B7">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <v>49</v>
+      </c>
+      <c r="D7">
+        <v>53</v>
+      </c>
+      <c r="E7">
+        <v>35</v>
+      </c>
+      <c r="F7">
+        <v>63</v>
+      </c>
+      <c r="G7">
+        <v>51</v>
+      </c>
+      <c r="H7">
+        <v>66</v>
+      </c>
+      <c r="I7">
+        <v>52</v>
+      </c>
+      <c r="J7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>60</v>
+      </c>
+      <c r="B8">
+        <v>52</v>
+      </c>
+      <c r="C8">
+        <v>46</v>
+      </c>
+      <c r="D8">
+        <v>46</v>
+      </c>
+      <c r="E8">
+        <v>39</v>
+      </c>
+      <c r="F8">
+        <v>53</v>
+      </c>
+      <c r="G8">
+        <v>45</v>
+      </c>
+      <c r="H8">
+        <v>52</v>
+      </c>
+      <c r="I8">
+        <v>50</v>
+      </c>
+      <c r="J8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>53</v>
+      </c>
+      <c r="B9">
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>51</v>
+      </c>
+      <c r="D9">
+        <v>57</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>49</v>
+      </c>
+      <c r="G9">
+        <v>52</v>
+      </c>
+      <c r="H9">
+        <v>50</v>
+      </c>
+      <c r="I9">
+        <v>56</v>
+      </c>
+      <c r="J9">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>51</v>
+      </c>
+      <c r="B10">
+        <v>53</v>
+      </c>
+      <c r="C10">
+        <v>45</v>
+      </c>
+      <c r="D10">
+        <v>55</v>
+      </c>
+      <c r="E10">
+        <v>53</v>
+      </c>
+      <c r="F10">
+        <v>66</v>
+      </c>
+      <c r="G10">
+        <v>45</v>
+      </c>
+      <c r="H10">
+        <v>54</v>
+      </c>
+      <c r="I10">
+        <v>53</v>
+      </c>
+      <c r="J10">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>